--- a/Projektdateien/Wochenplan_Sascha_Schulz.xlsx
+++ b/Projektdateien/Wochenplan_Sascha_Schulz.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8ee37c046c0b585d/Dokumente/WI/DOIT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schul\Documents\WI\DOIT\Projektdateien\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="11_B0C04488692624BBB935C976EEA2344496A21141" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DF0CCE2-55E1-4289-87F1-2924065658A6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C5602B-4528-4F77-AC2A-A4BD58DCF034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-78" yWindow="1458" windowWidth="22260" windowHeight="11694" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wochenplan (Woche 1)" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="61">
   <si>
     <t>Wochenplan: Woche 1</t>
   </si>
@@ -218,6 +218,15 @@
   </si>
   <si>
     <t>04.05 - 08.05.2026</t>
+  </si>
+  <si>
+    <t>Fehlersuche und anpassungen</t>
+  </si>
+  <si>
+    <t>Schulz Sascha</t>
+  </si>
+  <si>
+    <t>08.06 - 12-06.26</t>
   </si>
 </sst>
 </file>
@@ -493,7 +502,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -558,26 +567,34 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyProtection="1">
@@ -586,32 +603,30 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -629,10 +644,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -939,63 +950,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="37"/>
     </row>
     <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="36"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="38"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="39"/>
     </row>
     <row r="3" spans="1:17" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="39"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="41"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="42"/>
     </row>
     <row r="4" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2"/>
@@ -1017,11 +1028,11 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="43" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="24" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="23"/>
@@ -1031,16 +1042,16 @@
       <c r="H5" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="24">
         <v>19</v>
       </c>
       <c r="J5" s="23"/>
       <c r="K5" s="23"/>
-      <c r="L5" s="44" t="s">
+      <c r="L5" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="M5" s="37"/>
-      <c r="N5" s="45" t="s">
+      <c r="M5" s="29"/>
+      <c r="N5" s="30" t="s">
         <v>57</v>
       </c>
       <c r="O5" s="23"/>
@@ -1073,28 +1084,28 @@
       </c>
     </row>
     <row r="7" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
       <c r="P7" s="19"/>
       <c r="Q7" s="20"/>
     </row>
     <row r="8" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="26" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="23"/>
@@ -1110,7 +1121,7 @@
       <c r="L8" s="23"/>
       <c r="M8" s="23"/>
       <c r="N8" s="23"/>
-      <c r="O8" s="28"/>
+      <c r="O8" s="27"/>
       <c r="P8" s="7">
         <v>2</v>
       </c>
@@ -1119,7 +1130,7 @@
       </c>
     </row>
     <row r="9" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="45" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="23"/>
@@ -1135,7 +1146,7 @@
       <c r="L9" s="23"/>
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
-      <c r="O9" s="28"/>
+      <c r="O9" s="27"/>
       <c r="P9" s="5">
         <v>3</v>
       </c>
@@ -1144,7 +1155,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="26" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="23"/>
@@ -1160,7 +1171,7 @@
       <c r="L10" s="23"/>
       <c r="M10" s="23"/>
       <c r="N10" s="23"/>
-      <c r="O10" s="28"/>
+      <c r="O10" s="27"/>
       <c r="P10" s="7">
         <v>2</v>
       </c>
@@ -1169,7 +1180,7 @@
       </c>
     </row>
     <row r="11" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="45" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="23"/>
@@ -1185,12 +1196,12 @@
       <c r="L11" s="23"/>
       <c r="M11" s="23"/>
       <c r="N11" s="23"/>
-      <c r="O11" s="28"/>
+      <c r="O11" s="27"/>
       <c r="P11" s="5"/>
       <c r="Q11" s="9"/>
     </row>
     <row r="12" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="42"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
@@ -1204,12 +1215,12 @@
       <c r="L12" s="23"/>
       <c r="M12" s="23"/>
       <c r="N12" s="23"/>
-      <c r="O12" s="28"/>
+      <c r="O12" s="27"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="12"/>
     </row>
     <row r="13" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="22"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="23"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
@@ -1228,7 +1239,7 @@
       <c r="Q13" s="9"/>
     </row>
     <row r="14" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="42"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="23"/>
       <c r="C14" s="23"/>
       <c r="D14" s="23"/>
@@ -1242,52 +1253,52 @@
       <c r="L14" s="23"/>
       <c r="M14" s="23"/>
       <c r="N14" s="23"/>
-      <c r="O14" s="28"/>
+      <c r="O14" s="27"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="8"/>
     </row>
     <row r="15" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="29"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
+      <c r="A15" s="43"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
       <c r="P15" s="13"/>
       <c r="Q15" s="14"/>
     </row>
     <row r="16" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
       <c r="P16" s="19"/>
       <c r="Q16" s="20"/>
     </row>
     <row r="17" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="22" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="23"/>
@@ -1312,7 +1323,7 @@
       </c>
     </row>
     <row r="18" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="23"/>
@@ -1337,7 +1348,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="22" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="23"/>
@@ -1362,7 +1373,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="25" t="s">
         <v>16</v>
       </c>
       <c r="B20" s="23"/>
@@ -1383,7 +1394,7 @@
       <c r="Q20" s="9"/>
     </row>
     <row r="21" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="26"/>
+      <c r="A21" s="22"/>
       <c r="B21" s="23"/>
       <c r="C21" s="23"/>
       <c r="D21" s="23"/>
@@ -1402,7 +1413,7 @@
       <c r="Q21" s="12"/>
     </row>
     <row r="22" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="22"/>
+      <c r="A22" s="25"/>
       <c r="B22" s="23"/>
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
@@ -1421,7 +1432,7 @@
       <c r="Q22" s="9"/>
     </row>
     <row r="23" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="26"/>
+      <c r="A23" s="22"/>
       <c r="B23" s="23"/>
       <c r="C23" s="23"/>
       <c r="D23" s="23"/>
@@ -1440,47 +1451,47 @@
       <c r="Q23" s="12"/>
     </row>
     <row r="24" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="29"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
+      <c r="A24" s="43"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
       <c r="P24" s="13"/>
       <c r="Q24" s="14"/>
     </row>
     <row r="25" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="25"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="34"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="34"/>
       <c r="P25" s="19"/>
       <c r="Q25" s="20"/>
     </row>
     <row r="26" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="22" t="s">
         <v>18</v>
       </c>
       <c r="B26" s="23"/>
@@ -1505,7 +1516,7 @@
       </c>
     </row>
     <row r="27" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="25" t="s">
         <v>19</v>
       </c>
       <c r="B27" s="23"/>
@@ -1530,7 +1541,7 @@
       </c>
     </row>
     <row r="28" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="22" t="s">
         <v>20</v>
       </c>
       <c r="B28" s="23"/>
@@ -1555,7 +1566,7 @@
       </c>
     </row>
     <row r="29" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="25" t="s">
         <v>21</v>
       </c>
       <c r="B29" s="23"/>
@@ -1576,7 +1587,7 @@
       <c r="Q29" s="9"/>
     </row>
     <row r="30" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="26"/>
+      <c r="A30" s="22"/>
       <c r="B30" s="23"/>
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
@@ -1595,7 +1606,7 @@
       <c r="Q30" s="12"/>
     </row>
     <row r="31" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="22"/>
+      <c r="A31" s="25"/>
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
@@ -1614,7 +1625,7 @@
       <c r="Q31" s="9"/>
     </row>
     <row r="32" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="26"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="23"/>
       <c r="C32" s="23"/>
       <c r="D32" s="23"/>
@@ -1633,47 +1644,47 @@
       <c r="Q32" s="12"/>
     </row>
     <row r="33" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="29"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="30"/>
-      <c r="O33" s="30"/>
+      <c r="A33" s="43"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
       <c r="P33" s="13"/>
       <c r="Q33" s="14"/>
     </row>
     <row r="34" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="34"/>
+      <c r="N34" s="34"/>
+      <c r="O34" s="34"/>
       <c r="P34" s="19"/>
       <c r="Q34" s="20"/>
     </row>
     <row r="35" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="22" t="s">
         <v>23</v>
       </c>
       <c r="B35" s="23"/>
@@ -1694,7 +1705,7 @@
       <c r="Q35" s="8"/>
     </row>
     <row r="36" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="22"/>
+      <c r="A36" s="25"/>
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
       <c r="D36" s="23"/>
@@ -1713,7 +1724,7 @@
       <c r="Q36" s="9"/>
     </row>
     <row r="37" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="26"/>
+      <c r="A37" s="22"/>
       <c r="B37" s="23"/>
       <c r="C37" s="23"/>
       <c r="D37" s="23"/>
@@ -1732,7 +1743,7 @@
       <c r="Q37" s="8"/>
     </row>
     <row r="38" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="22"/>
+      <c r="A38" s="25"/>
       <c r="B38" s="23"/>
       <c r="C38" s="23"/>
       <c r="D38" s="23"/>
@@ -1751,7 +1762,7 @@
       <c r="Q38" s="9"/>
     </row>
     <row r="39" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="26"/>
+      <c r="A39" s="22"/>
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
@@ -1770,7 +1781,7 @@
       <c r="Q39" s="8"/>
     </row>
     <row r="40" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="22"/>
+      <c r="A40" s="25"/>
       <c r="B40" s="23"/>
       <c r="C40" s="23"/>
       <c r="D40" s="23"/>
@@ -1789,7 +1800,7 @@
       <c r="Q40" s="9"/>
     </row>
     <row r="41" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="26"/>
+      <c r="A41" s="22"/>
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
       <c r="D41" s="23"/>
@@ -1808,47 +1819,47 @@
       <c r="Q41" s="8"/>
     </row>
     <row r="42" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="29"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
-      <c r="K42" s="30"/>
-      <c r="L42" s="30"/>
-      <c r="M42" s="30"/>
-      <c r="N42" s="30"/>
-      <c r="O42" s="30"/>
+      <c r="A42" s="43"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
       <c r="P42" s="13"/>
       <c r="Q42" s="14"/>
     </row>
     <row r="43" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="24" t="s">
+      <c r="A43" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="25"/>
-      <c r="J43" s="25"/>
-      <c r="K43" s="25"/>
-      <c r="L43" s="25"/>
-      <c r="M43" s="25"/>
-      <c r="N43" s="25"/>
-      <c r="O43" s="25"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
+      <c r="L43" s="34"/>
+      <c r="M43" s="34"/>
+      <c r="N43" s="34"/>
+      <c r="O43" s="34"/>
       <c r="P43" s="19"/>
       <c r="Q43" s="20"/>
     </row>
     <row r="44" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="26" t="s">
+      <c r="A44" s="22" t="s">
         <v>23</v>
       </c>
       <c r="B44" s="23"/>
@@ -1869,7 +1880,7 @@
       <c r="Q44" s="8"/>
     </row>
     <row r="45" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="22"/>
+      <c r="A45" s="25"/>
       <c r="B45" s="23"/>
       <c r="C45" s="23"/>
       <c r="D45" s="23"/>
@@ -1888,21 +1899,21 @@
       <c r="Q45" s="9"/>
     </row>
     <row r="46" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="32"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
+      <c r="A46" s="31"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="32"/>
+      <c r="O46" s="32"/>
       <c r="P46" s="6"/>
       <c r="Q46" s="10"/>
     </row>
@@ -2083,33 +2094,14 @@
     <row r="195" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="A46:O46"/>
-    <mergeCell ref="A37:O37"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="D43:O43"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A38:O38"/>
-    <mergeCell ref="A28:O28"/>
-    <mergeCell ref="A44:O44"/>
-    <mergeCell ref="A31:O31"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A40:O40"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="A39:O39"/>
-    <mergeCell ref="D34:O34"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="D7:O7"/>
-    <mergeCell ref="A21:O21"/>
-    <mergeCell ref="D16:O16"/>
-    <mergeCell ref="A20:O20"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A19:O19"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A9:O9"/>
-    <mergeCell ref="A15:O15"/>
-    <mergeCell ref="N5:Q5"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="A45:O45"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A41:O41"/>
     <mergeCell ref="A1:Q3"/>
     <mergeCell ref="A26:O26"/>
     <mergeCell ref="A12:O12"/>
@@ -2126,14 +2118,33 @@
     <mergeCell ref="D25:O25"/>
     <mergeCell ref="A35:O35"/>
     <mergeCell ref="A29:O29"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="A11:O11"/>
-    <mergeCell ref="A45:O45"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A41:O41"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="D7:O7"/>
+    <mergeCell ref="A21:O21"/>
+    <mergeCell ref="D16:O16"/>
+    <mergeCell ref="A20:O20"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A9:O9"/>
+    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="N5:Q5"/>
+    <mergeCell ref="A46:O46"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="D43:O43"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A38:O38"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A44:O44"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A40:O40"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="A39:O39"/>
+    <mergeCell ref="D34:O34"/>
   </mergeCells>
   <pageMargins left="0.62992125984251968" right="0.39370078740157483" top="0.78740157480314965" bottom="0.39370078740157483" header="0.39370078740157483" footer="0"/>
   <pageSetup paperSize="9" scale="99" orientation="portrait"/>
@@ -2159,63 +2170,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="37"/>
     </row>
     <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="36"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="38"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="39"/>
     </row>
     <row r="3" spans="1:17" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="39"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="41"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="42"/>
     </row>
     <row r="4" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2"/>
@@ -2237,11 +2248,11 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="43" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="24" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="23"/>
@@ -2251,16 +2262,16 @@
       <c r="H5" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="24">
         <v>20</v>
       </c>
       <c r="J5" s="23"/>
       <c r="K5" s="23"/>
-      <c r="L5" s="44" t="s">
+      <c r="L5" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="M5" s="37"/>
-      <c r="N5" s="45" t="s">
+      <c r="M5" s="29"/>
+      <c r="N5" s="30" t="s">
         <v>56</v>
       </c>
       <c r="O5" s="23"/>
@@ -2293,28 +2304,28 @@
       </c>
     </row>
     <row r="7" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
       <c r="P7" s="19"/>
       <c r="Q7" s="20"/>
     </row>
     <row r="8" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="26" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="23"/>
@@ -2330,7 +2341,7 @@
       <c r="L8" s="23"/>
       <c r="M8" s="23"/>
       <c r="N8" s="23"/>
-      <c r="O8" s="28"/>
+      <c r="O8" s="27"/>
       <c r="P8" s="7">
         <v>2</v>
       </c>
@@ -2339,7 +2350,7 @@
       </c>
     </row>
     <row r="9" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="45" t="s">
         <v>28</v>
       </c>
       <c r="B9" s="23"/>
@@ -2355,7 +2366,7 @@
       <c r="L9" s="23"/>
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
-      <c r="O9" s="28"/>
+      <c r="O9" s="27"/>
       <c r="P9" s="5">
         <v>3</v>
       </c>
@@ -2364,7 +2375,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="26" t="s">
         <v>52</v>
       </c>
       <c r="B10" s="23"/>
@@ -2380,7 +2391,7 @@
       <c r="L10" s="23"/>
       <c r="M10" s="23"/>
       <c r="N10" s="23"/>
-      <c r="O10" s="28"/>
+      <c r="O10" s="27"/>
       <c r="P10" s="7">
         <v>2</v>
       </c>
@@ -2389,7 +2400,7 @@
       </c>
     </row>
     <row r="11" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="45" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="23"/>
@@ -2405,12 +2416,12 @@
       <c r="L11" s="23"/>
       <c r="M11" s="23"/>
       <c r="N11" s="23"/>
-      <c r="O11" s="28"/>
+      <c r="O11" s="27"/>
       <c r="P11" s="5"/>
       <c r="Q11" s="9"/>
     </row>
     <row r="12" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="42"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
@@ -2424,12 +2435,12 @@
       <c r="L12" s="23"/>
       <c r="M12" s="23"/>
       <c r="N12" s="23"/>
-      <c r="O12" s="28"/>
+      <c r="O12" s="27"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="12"/>
     </row>
     <row r="13" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="22"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="23"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
@@ -2448,7 +2459,7 @@
       <c r="Q13" s="9"/>
     </row>
     <row r="14" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="42"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="23"/>
       <c r="C14" s="23"/>
       <c r="D14" s="23"/>
@@ -2462,52 +2473,52 @@
       <c r="L14" s="23"/>
       <c r="M14" s="23"/>
       <c r="N14" s="23"/>
-      <c r="O14" s="28"/>
+      <c r="O14" s="27"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="8"/>
     </row>
     <row r="15" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="29"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
+      <c r="A15" s="43"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
       <c r="P15" s="13"/>
       <c r="Q15" s="14"/>
     </row>
     <row r="16" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
       <c r="P16" s="19"/>
       <c r="Q16" s="20"/>
     </row>
     <row r="17" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="22" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="23"/>
@@ -2528,7 +2539,7 @@
       <c r="Q17" s="8"/>
     </row>
     <row r="18" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="22"/>
+      <c r="A18" s="25"/>
       <c r="B18" s="23"/>
       <c r="C18" s="23"/>
       <c r="D18" s="23"/>
@@ -2547,7 +2558,7 @@
       <c r="Q18" s="14"/>
     </row>
     <row r="19" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="26"/>
+      <c r="A19" s="22"/>
       <c r="B19" s="23"/>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
@@ -2566,7 +2577,7 @@
       <c r="Q19" s="8"/>
     </row>
     <row r="20" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="22"/>
+      <c r="A20" s="25"/>
       <c r="B20" s="23"/>
       <c r="C20" s="23"/>
       <c r="D20" s="23"/>
@@ -2585,7 +2596,7 @@
       <c r="Q20" s="9"/>
     </row>
     <row r="21" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="26"/>
+      <c r="A21" s="22"/>
       <c r="B21" s="23"/>
       <c r="C21" s="23"/>
       <c r="D21" s="23"/>
@@ -2604,7 +2615,7 @@
       <c r="Q21" s="12"/>
     </row>
     <row r="22" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="22"/>
+      <c r="A22" s="25"/>
       <c r="B22" s="23"/>
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
@@ -2623,7 +2634,7 @@
       <c r="Q22" s="9"/>
     </row>
     <row r="23" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="26"/>
+      <c r="A23" s="22"/>
       <c r="B23" s="23"/>
       <c r="C23" s="23"/>
       <c r="D23" s="23"/>
@@ -2642,47 +2653,47 @@
       <c r="Q23" s="12"/>
     </row>
     <row r="24" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="29"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
+      <c r="A24" s="43"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
       <c r="P24" s="13"/>
       <c r="Q24" s="14"/>
     </row>
     <row r="25" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="25"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="34"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="34"/>
       <c r="P25" s="19"/>
       <c r="Q25" s="20"/>
     </row>
     <row r="26" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="22" t="s">
         <v>23</v>
       </c>
       <c r="B26" s="23"/>
@@ -2703,7 +2714,7 @@
       <c r="Q26" s="8"/>
     </row>
     <row r="27" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="22"/>
+      <c r="A27" s="25"/>
       <c r="B27" s="23"/>
       <c r="C27" s="23"/>
       <c r="D27" s="23"/>
@@ -2722,7 +2733,7 @@
       <c r="Q27" s="14"/>
     </row>
     <row r="28" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="26"/>
+      <c r="A28" s="22"/>
       <c r="B28" s="23"/>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
@@ -2741,7 +2752,7 @@
       <c r="Q28" s="8"/>
     </row>
     <row r="29" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="22"/>
+      <c r="A29" s="25"/>
       <c r="B29" s="23"/>
       <c r="C29" s="23"/>
       <c r="D29" s="23"/>
@@ -2760,7 +2771,7 @@
       <c r="Q29" s="9"/>
     </row>
     <row r="30" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="26"/>
+      <c r="A30" s="22"/>
       <c r="B30" s="23"/>
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
@@ -2779,7 +2790,7 @@
       <c r="Q30" s="12"/>
     </row>
     <row r="31" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="22"/>
+      <c r="A31" s="25"/>
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
@@ -2798,7 +2809,7 @@
       <c r="Q31" s="9"/>
     </row>
     <row r="32" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="26"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="23"/>
       <c r="C32" s="23"/>
       <c r="D32" s="23"/>
@@ -2817,47 +2828,47 @@
       <c r="Q32" s="12"/>
     </row>
     <row r="33" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="29"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="30"/>
-      <c r="O33" s="30"/>
+      <c r="A33" s="43"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
       <c r="P33" s="13"/>
       <c r="Q33" s="14"/>
     </row>
     <row r="34" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="34"/>
+      <c r="N34" s="34"/>
+      <c r="O34" s="34"/>
       <c r="P34" s="19"/>
       <c r="Q34" s="20"/>
     </row>
     <row r="35" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="22" t="s">
         <v>30</v>
       </c>
       <c r="B35" s="23"/>
@@ -2878,7 +2889,7 @@
       <c r="Q35" s="8"/>
     </row>
     <row r="36" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="22"/>
+      <c r="A36" s="25"/>
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
       <c r="D36" s="23"/>
@@ -2897,7 +2908,7 @@
       <c r="Q36" s="9"/>
     </row>
     <row r="37" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="26"/>
+      <c r="A37" s="22"/>
       <c r="B37" s="23"/>
       <c r="C37" s="23"/>
       <c r="D37" s="23"/>
@@ -2916,7 +2927,7 @@
       <c r="Q37" s="8"/>
     </row>
     <row r="38" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="22"/>
+      <c r="A38" s="25"/>
       <c r="B38" s="23"/>
       <c r="C38" s="23"/>
       <c r="D38" s="23"/>
@@ -2935,7 +2946,7 @@
       <c r="Q38" s="9"/>
     </row>
     <row r="39" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="26"/>
+      <c r="A39" s="22"/>
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
@@ -2954,7 +2965,7 @@
       <c r="Q39" s="8"/>
     </row>
     <row r="40" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="22"/>
+      <c r="A40" s="25"/>
       <c r="B40" s="23"/>
       <c r="C40" s="23"/>
       <c r="D40" s="23"/>
@@ -2973,7 +2984,7 @@
       <c r="Q40" s="9"/>
     </row>
     <row r="41" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="26"/>
+      <c r="A41" s="22"/>
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
       <c r="D41" s="23"/>
@@ -2992,47 +3003,47 @@
       <c r="Q41" s="8"/>
     </row>
     <row r="42" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="29"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
-      <c r="K42" s="30"/>
-      <c r="L42" s="30"/>
-      <c r="M42" s="30"/>
-      <c r="N42" s="30"/>
-      <c r="O42" s="30"/>
+      <c r="A42" s="43"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
       <c r="P42" s="13"/>
       <c r="Q42" s="14"/>
     </row>
     <row r="43" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="24" t="s">
+      <c r="A43" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="25"/>
-      <c r="J43" s="25"/>
-      <c r="K43" s="25"/>
-      <c r="L43" s="25"/>
-      <c r="M43" s="25"/>
-      <c r="N43" s="25"/>
-      <c r="O43" s="25"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
+      <c r="L43" s="34"/>
+      <c r="M43" s="34"/>
+      <c r="N43" s="34"/>
+      <c r="O43" s="34"/>
       <c r="P43" s="19"/>
       <c r="Q43" s="20"/>
     </row>
     <row r="44" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="26" t="s">
+      <c r="A44" s="22" t="s">
         <v>30</v>
       </c>
       <c r="B44" s="23"/>
@@ -3053,7 +3064,7 @@
       <c r="Q44" s="8"/>
     </row>
     <row r="45" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="22"/>
+      <c r="A45" s="25"/>
       <c r="B45" s="23"/>
       <c r="C45" s="23"/>
       <c r="D45" s="23"/>
@@ -3072,21 +3083,21 @@
       <c r="Q45" s="9"/>
     </row>
     <row r="46" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="32"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
+      <c r="A46" s="31"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="32"/>
+      <c r="O46" s="32"/>
       <c r="P46" s="6"/>
       <c r="Q46" s="10"/>
     </row>
@@ -3267,18 +3278,25 @@
     <row r="195" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="A41:O41"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="A37:O37"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="A8:O8"/>
-    <mergeCell ref="A22:O22"/>
-    <mergeCell ref="A17:O17"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="A19:O19"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="N5:Q5"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A38:O38"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A45:O45"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A44:O44"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A40:O40"/>
+    <mergeCell ref="A9:O9"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="A39:O39"/>
+    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="D34:O34"/>
+    <mergeCell ref="A24:O24"/>
     <mergeCell ref="A46:O46"/>
     <mergeCell ref="A18:O18"/>
     <mergeCell ref="D7:O7"/>
@@ -3295,29 +3313,22 @@
     <mergeCell ref="A23:O23"/>
     <mergeCell ref="A32:O32"/>
     <mergeCell ref="L5:M5"/>
+    <mergeCell ref="A41:O41"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="A8:O8"/>
+    <mergeCell ref="A22:O22"/>
+    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="N5:Q5"/>
     <mergeCell ref="D25:O25"/>
     <mergeCell ref="A29:O29"/>
     <mergeCell ref="A35:O35"/>
     <mergeCell ref="A20:O20"/>
-    <mergeCell ref="A38:O38"/>
-    <mergeCell ref="A28:O28"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A45:O45"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A44:O44"/>
-    <mergeCell ref="A31:O31"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A40:O40"/>
-    <mergeCell ref="A9:O9"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="A39:O39"/>
-    <mergeCell ref="A15:O15"/>
-    <mergeCell ref="D34:O34"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="A11:O11"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <pageMargins left="0.62992125984251968" right="0.39370078740157483" top="0.78740157480314965" bottom="0.39370078740157483" header="0.39370078740157483" footer="0"/>
   <pageSetup paperSize="9" scale="99" orientation="portrait"/>
@@ -3343,63 +3354,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="37"/>
     </row>
     <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="36"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="38"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="39"/>
     </row>
     <row r="3" spans="1:17" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="39"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="41"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="42"/>
     </row>
     <row r="4" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2"/>
@@ -3421,11 +3432,11 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="43" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="24" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="23"/>
@@ -3435,16 +3446,16 @@
       <c r="H5" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="24">
         <v>21</v>
       </c>
       <c r="J5" s="23"/>
       <c r="K5" s="23"/>
-      <c r="L5" s="44" t="s">
+      <c r="L5" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="M5" s="37"/>
-      <c r="N5" s="45" t="s">
+      <c r="M5" s="29"/>
+      <c r="N5" s="30" t="s">
         <v>55</v>
       </c>
       <c r="O5" s="23"/>
@@ -3477,28 +3488,28 @@
       </c>
     </row>
     <row r="7" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
       <c r="P7" s="19"/>
       <c r="Q7" s="20"/>
     </row>
     <row r="8" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="26" t="s">
         <v>53</v>
       </c>
       <c r="B8" s="23"/>
@@ -3514,14 +3525,14 @@
       <c r="L8" s="23"/>
       <c r="M8" s="23"/>
       <c r="N8" s="23"/>
-      <c r="O8" s="28"/>
+      <c r="O8" s="27"/>
       <c r="P8" s="7">
         <v>1</v>
       </c>
       <c r="Q8" s="8"/>
     </row>
     <row r="9" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="45" t="s">
         <v>32</v>
       </c>
       <c r="B9" s="23"/>
@@ -3537,14 +3548,14 @@
       <c r="L9" s="23"/>
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
-      <c r="O9" s="28"/>
+      <c r="O9" s="27"/>
       <c r="P9" s="5">
         <v>5</v>
       </c>
       <c r="Q9" s="9"/>
     </row>
     <row r="10" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="26" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="23"/>
@@ -3560,14 +3571,14 @@
       <c r="L10" s="23"/>
       <c r="M10" s="23"/>
       <c r="N10" s="23"/>
-      <c r="O10" s="28"/>
+      <c r="O10" s="27"/>
       <c r="P10" s="7">
         <v>1</v>
       </c>
       <c r="Q10" s="8"/>
     </row>
     <row r="11" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="45" t="s">
         <v>34</v>
       </c>
       <c r="B11" s="23"/>
@@ -3583,12 +3594,12 @@
       <c r="L11" s="23"/>
       <c r="M11" s="23"/>
       <c r="N11" s="23"/>
-      <c r="O11" s="28"/>
+      <c r="O11" s="27"/>
       <c r="P11" s="5"/>
       <c r="Q11" s="9"/>
     </row>
     <row r="12" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="42"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
@@ -3602,12 +3613,12 @@
       <c r="L12" s="23"/>
       <c r="M12" s="23"/>
       <c r="N12" s="23"/>
-      <c r="O12" s="28"/>
+      <c r="O12" s="27"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="12"/>
     </row>
     <row r="13" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="22"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="23"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
@@ -3626,7 +3637,7 @@
       <c r="Q13" s="9"/>
     </row>
     <row r="14" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="42"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="23"/>
       <c r="C14" s="23"/>
       <c r="D14" s="23"/>
@@ -3640,52 +3651,52 @@
       <c r="L14" s="23"/>
       <c r="M14" s="23"/>
       <c r="N14" s="23"/>
-      <c r="O14" s="28"/>
+      <c r="O14" s="27"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="8"/>
     </row>
     <row r="15" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="29"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
+      <c r="A15" s="43"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
       <c r="P15" s="13"/>
       <c r="Q15" s="14"/>
     </row>
     <row r="16" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
       <c r="P16" s="19"/>
       <c r="Q16" s="20"/>
     </row>
     <row r="17" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="22" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="23"/>
@@ -3708,7 +3719,7 @@
       <c r="Q17" s="8"/>
     </row>
     <row r="18" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="25" t="s">
         <v>36</v>
       </c>
       <c r="B18" s="23"/>
@@ -3731,7 +3742,7 @@
       <c r="Q18" s="14"/>
     </row>
     <row r="19" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="22" t="s">
         <v>54</v>
       </c>
       <c r="B19" s="23"/>
@@ -3754,7 +3765,7 @@
       <c r="Q19" s="8"/>
     </row>
     <row r="20" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="25" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="23"/>
@@ -3775,7 +3786,7 @@
       <c r="Q20" s="9"/>
     </row>
     <row r="21" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="26"/>
+      <c r="A21" s="22"/>
       <c r="B21" s="23"/>
       <c r="C21" s="23"/>
       <c r="D21" s="23"/>
@@ -3794,7 +3805,7 @@
       <c r="Q21" s="12"/>
     </row>
     <row r="22" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="22"/>
+      <c r="A22" s="25"/>
       <c r="B22" s="23"/>
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
@@ -3813,7 +3824,7 @@
       <c r="Q22" s="9"/>
     </row>
     <row r="23" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="26"/>
+      <c r="A23" s="22"/>
       <c r="B23" s="23"/>
       <c r="C23" s="23"/>
       <c r="D23" s="23"/>
@@ -3832,47 +3843,47 @@
       <c r="Q23" s="12"/>
     </row>
     <row r="24" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="29"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
+      <c r="A24" s="43"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
       <c r="P24" s="13"/>
       <c r="Q24" s="14"/>
     </row>
     <row r="25" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="25"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="34"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="34"/>
       <c r="P25" s="19"/>
       <c r="Q25" s="20"/>
     </row>
     <row r="26" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="22" t="s">
         <v>38</v>
       </c>
       <c r="B26" s="23"/>
@@ -3895,7 +3906,7 @@
       <c r="Q26" s="8"/>
     </row>
     <row r="27" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="25" t="s">
         <v>39</v>
       </c>
       <c r="B27" s="23"/>
@@ -3918,7 +3929,7 @@
       <c r="Q27" s="14"/>
     </row>
     <row r="28" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="22" t="s">
         <v>40</v>
       </c>
       <c r="B28" s="23"/>
@@ -3941,7 +3952,7 @@
       <c r="Q28" s="8"/>
     </row>
     <row r="29" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="25" t="s">
         <v>41</v>
       </c>
       <c r="B29" s="23"/>
@@ -3962,7 +3973,7 @@
       <c r="Q29" s="9"/>
     </row>
     <row r="30" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="26"/>
+      <c r="A30" s="22"/>
       <c r="B30" s="23"/>
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
@@ -3981,7 +3992,7 @@
       <c r="Q30" s="12"/>
     </row>
     <row r="31" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="22"/>
+      <c r="A31" s="25"/>
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
@@ -4000,7 +4011,7 @@
       <c r="Q31" s="9"/>
     </row>
     <row r="32" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="26"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="23"/>
       <c r="C32" s="23"/>
       <c r="D32" s="23"/>
@@ -4019,47 +4030,47 @@
       <c r="Q32" s="12"/>
     </row>
     <row r="33" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="29"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="30"/>
-      <c r="O33" s="30"/>
+      <c r="A33" s="43"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
       <c r="P33" s="13"/>
       <c r="Q33" s="14"/>
     </row>
     <row r="34" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="34"/>
+      <c r="N34" s="34"/>
+      <c r="O34" s="34"/>
       <c r="P34" s="19"/>
       <c r="Q34" s="20"/>
     </row>
     <row r="35" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="22" t="s">
         <v>42</v>
       </c>
       <c r="B35" s="23"/>
@@ -4082,7 +4093,7 @@
       <c r="Q35" s="8"/>
     </row>
     <row r="36" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="25" t="s">
         <v>43</v>
       </c>
       <c r="B36" s="23"/>
@@ -4105,7 +4116,7 @@
       <c r="Q36" s="9"/>
     </row>
     <row r="37" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="26" t="s">
+      <c r="A37" s="22" t="s">
         <v>44</v>
       </c>
       <c r="B37" s="23"/>
@@ -4128,7 +4139,7 @@
       <c r="Q37" s="8"/>
     </row>
     <row r="38" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="25" t="s">
         <v>45</v>
       </c>
       <c r="B38" s="23"/>
@@ -4149,7 +4160,7 @@
       <c r="Q38" s="9"/>
     </row>
     <row r="39" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="26"/>
+      <c r="A39" s="22"/>
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
@@ -4168,7 +4179,7 @@
       <c r="Q39" s="8"/>
     </row>
     <row r="40" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="22"/>
+      <c r="A40" s="25"/>
       <c r="B40" s="23"/>
       <c r="C40" s="23"/>
       <c r="D40" s="23"/>
@@ -4187,7 +4198,7 @@
       <c r="Q40" s="9"/>
     </row>
     <row r="41" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="26"/>
+      <c r="A41" s="22"/>
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
       <c r="D41" s="23"/>
@@ -4206,47 +4217,47 @@
       <c r="Q41" s="8"/>
     </row>
     <row r="42" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="29"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
-      <c r="K42" s="30"/>
-      <c r="L42" s="30"/>
-      <c r="M42" s="30"/>
-      <c r="N42" s="30"/>
-      <c r="O42" s="30"/>
+      <c r="A42" s="43"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
       <c r="P42" s="13"/>
       <c r="Q42" s="14"/>
     </row>
     <row r="43" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="24" t="s">
+      <c r="A43" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="25"/>
-      <c r="J43" s="25"/>
-      <c r="K43" s="25"/>
-      <c r="L43" s="25"/>
-      <c r="M43" s="25"/>
-      <c r="N43" s="25"/>
-      <c r="O43" s="25"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
+      <c r="L43" s="34"/>
+      <c r="M43" s="34"/>
+      <c r="N43" s="34"/>
+      <c r="O43" s="34"/>
       <c r="P43" s="19"/>
       <c r="Q43" s="20"/>
     </row>
     <row r="44" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="26" t="s">
+      <c r="A44" s="22" t="s">
         <v>46</v>
       </c>
       <c r="B44" s="23"/>
@@ -4269,7 +4280,7 @@
       <c r="Q44" s="8"/>
     </row>
     <row r="45" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="22" t="s">
+      <c r="A45" s="25" t="s">
         <v>47</v>
       </c>
       <c r="B45" s="23"/>
@@ -4292,21 +4303,21 @@
       <c r="Q45" s="9"/>
     </row>
     <row r="46" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="32"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
+      <c r="A46" s="31"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="32"/>
+      <c r="O46" s="32"/>
       <c r="P46" s="6"/>
       <c r="Q46" s="10"/>
     </row>
@@ -4487,18 +4498,25 @@
     <row r="195" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="A41:O41"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="A37:O37"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="A8:O8"/>
-    <mergeCell ref="A22:O22"/>
-    <mergeCell ref="A17:O17"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="A19:O19"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="N5:Q5"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A38:O38"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A45:O45"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A44:O44"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A40:O40"/>
+    <mergeCell ref="A9:O9"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="A39:O39"/>
+    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="D34:O34"/>
+    <mergeCell ref="A24:O24"/>
     <mergeCell ref="A46:O46"/>
     <mergeCell ref="A18:O18"/>
     <mergeCell ref="D7:O7"/>
@@ -4515,29 +4533,22 @@
     <mergeCell ref="A23:O23"/>
     <mergeCell ref="A32:O32"/>
     <mergeCell ref="L5:M5"/>
+    <mergeCell ref="A41:O41"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="A8:O8"/>
+    <mergeCell ref="A22:O22"/>
+    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="N5:Q5"/>
     <mergeCell ref="D25:O25"/>
     <mergeCell ref="A29:O29"/>
     <mergeCell ref="A35:O35"/>
     <mergeCell ref="A20:O20"/>
-    <mergeCell ref="A38:O38"/>
-    <mergeCell ref="A28:O28"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A45:O45"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A44:O44"/>
-    <mergeCell ref="A31:O31"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A40:O40"/>
-    <mergeCell ref="A9:O9"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="A39:O39"/>
-    <mergeCell ref="A15:O15"/>
-    <mergeCell ref="D34:O34"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="A11:O11"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <pageMargins left="0.62992125984251968" right="0.39370078740157483" top="0.78740157480314965" bottom="0.39370078740157483" header="0.39370078740157483" footer="0"/>
   <pageSetup paperSize="9" scale="99" orientation="portrait"/>
@@ -4563,63 +4574,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="37"/>
     </row>
     <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="36"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="38"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="39"/>
     </row>
     <row r="3" spans="1:17" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="39"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="41"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="42"/>
     </row>
     <row r="4" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2"/>
@@ -4641,11 +4652,13 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="43"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="24" t="s">
+        <v>59</v>
+      </c>
       <c r="D5" s="23"/>
       <c r="E5" s="23"/>
       <c r="F5" s="23"/>
@@ -4653,14 +4666,18 @@
       <c r="H5" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="43"/>
+      <c r="I5" s="24">
+        <v>24</v>
+      </c>
       <c r="J5" s="23"/>
       <c r="K5" s="23"/>
-      <c r="L5" s="44" t="s">
+      <c r="L5" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="M5" s="37"/>
-      <c r="N5" s="45"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="30" t="s">
+        <v>60</v>
+      </c>
       <c r="O5" s="23"/>
       <c r="P5" s="23"/>
       <c r="Q5" s="23"/>
@@ -4691,28 +4708,30 @@
       </c>
     </row>
     <row r="7" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
       <c r="P7" s="19"/>
       <c r="Q7" s="20"/>
     </row>
     <row r="8" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="42"/>
+      <c r="A8" s="26" t="s">
+        <v>32</v>
+      </c>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
@@ -4726,31 +4745,39 @@
       <c r="L8" s="23"/>
       <c r="M8" s="23"/>
       <c r="N8" s="23"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="7"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="7">
+        <v>1</v>
+      </c>
       <c r="Q8" s="8"/>
     </row>
     <row r="9" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="27"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="5"/>
+      <c r="A9" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="5">
+        <v>1</v>
+      </c>
       <c r="Q9" s="9"/>
     </row>
     <row r="10" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="42"/>
+      <c r="A10" s="26" t="s">
+        <v>44</v>
+      </c>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
@@ -4764,12 +4791,16 @@
       <c r="L10" s="23"/>
       <c r="M10" s="23"/>
       <c r="N10" s="23"/>
-      <c r="O10" s="28"/>
-      <c r="P10" s="7"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="7">
+        <v>1</v>
+      </c>
       <c r="Q10" s="8"/>
     </row>
     <row r="11" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="27"/>
+      <c r="A11" s="45" t="s">
+        <v>58</v>
+      </c>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
@@ -4783,12 +4814,14 @@
       <c r="L11" s="23"/>
       <c r="M11" s="23"/>
       <c r="N11" s="23"/>
-      <c r="O11" s="28"/>
-      <c r="P11" s="5"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="5">
+        <v>4</v>
+      </c>
       <c r="Q11" s="9"/>
     </row>
     <row r="12" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="42"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
@@ -4802,12 +4835,12 @@
       <c r="L12" s="23"/>
       <c r="M12" s="23"/>
       <c r="N12" s="23"/>
-      <c r="O12" s="28"/>
+      <c r="O12" s="27"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="12"/>
     </row>
     <row r="13" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="22"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="23"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
@@ -4826,7 +4859,7 @@
       <c r="Q13" s="9"/>
     </row>
     <row r="14" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="42"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="23"/>
       <c r="C14" s="23"/>
       <c r="D14" s="23"/>
@@ -4840,52 +4873,54 @@
       <c r="L14" s="23"/>
       <c r="M14" s="23"/>
       <c r="N14" s="23"/>
-      <c r="O14" s="28"/>
+      <c r="O14" s="27"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="8"/>
     </row>
     <row r="15" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="29"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
+      <c r="A15" s="43"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
       <c r="P15" s="13"/>
       <c r="Q15" s="14"/>
     </row>
     <row r="16" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
       <c r="P16" s="19"/>
       <c r="Q16" s="20"/>
     </row>
     <row r="17" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="26"/>
+      <c r="A17" s="26" t="s">
+        <v>32</v>
+      </c>
       <c r="B17" s="23"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
@@ -4899,31 +4934,39 @@
       <c r="L17" s="23"/>
       <c r="M17" s="23"/>
       <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="7"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="7">
+        <v>1</v>
+      </c>
       <c r="Q17" s="8"/>
     </row>
     <row r="18" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="22"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="13"/>
+      <c r="A18" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="46"/>
+      <c r="K18" s="46"/>
+      <c r="L18" s="46"/>
+      <c r="M18" s="46"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="47"/>
+      <c r="P18" s="5">
+        <v>1</v>
+      </c>
       <c r="Q18" s="14"/>
     </row>
     <row r="19" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="26"/>
+      <c r="A19" s="26" t="s">
+        <v>44</v>
+      </c>
       <c r="B19" s="23"/>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
@@ -4937,12 +4980,16 @@
       <c r="L19" s="23"/>
       <c r="M19" s="23"/>
       <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="7"/>
+      <c r="O19" s="27"/>
+      <c r="P19" s="7">
+        <v>1</v>
+      </c>
       <c r="Q19" s="8"/>
     </row>
     <row r="20" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="22"/>
+      <c r="A20" s="45" t="s">
+        <v>58</v>
+      </c>
       <c r="B20" s="23"/>
       <c r="C20" s="23"/>
       <c r="D20" s="23"/>
@@ -4956,12 +5003,14 @@
       <c r="L20" s="23"/>
       <c r="M20" s="23"/>
       <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="5"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="5">
+        <v>4</v>
+      </c>
       <c r="Q20" s="9"/>
     </row>
     <row r="21" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="26"/>
+      <c r="A21" s="22"/>
       <c r="B21" s="23"/>
       <c r="C21" s="23"/>
       <c r="D21" s="23"/>
@@ -4980,7 +5029,7 @@
       <c r="Q21" s="12"/>
     </row>
     <row r="22" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="22"/>
+      <c r="A22" s="25"/>
       <c r="B22" s="23"/>
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
@@ -4999,7 +5048,7 @@
       <c r="Q22" s="9"/>
     </row>
     <row r="23" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="26"/>
+      <c r="A23" s="22"/>
       <c r="B23" s="23"/>
       <c r="C23" s="23"/>
       <c r="D23" s="23"/>
@@ -5018,47 +5067,49 @@
       <c r="Q23" s="12"/>
     </row>
     <row r="24" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="29"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
+      <c r="A24" s="43"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
       <c r="P24" s="13"/>
       <c r="Q24" s="14"/>
     </row>
     <row r="25" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="25"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="34"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="34"/>
       <c r="P25" s="19"/>
       <c r="Q25" s="20"/>
     </row>
     <row r="26" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="26"/>
+      <c r="A26" s="26" t="s">
+        <v>32</v>
+      </c>
       <c r="B26" s="23"/>
       <c r="C26" s="23"/>
       <c r="D26" s="23"/>
@@ -5072,31 +5123,39 @@
       <c r="L26" s="23"/>
       <c r="M26" s="23"/>
       <c r="N26" s="23"/>
-      <c r="O26" s="23"/>
-      <c r="P26" s="7"/>
+      <c r="O26" s="27"/>
+      <c r="P26" s="7">
+        <v>1</v>
+      </c>
       <c r="Q26" s="8"/>
     </row>
     <row r="27" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="22"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="23"/>
-      <c r="O27" s="23"/>
-      <c r="P27" s="13"/>
+      <c r="A27" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="46"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="47"/>
+      <c r="P27" s="5">
+        <v>1</v>
+      </c>
       <c r="Q27" s="14"/>
     </row>
     <row r="28" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="26"/>
+      <c r="A28" s="26" t="s">
+        <v>44</v>
+      </c>
       <c r="B28" s="23"/>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
@@ -5110,12 +5169,16 @@
       <c r="L28" s="23"/>
       <c r="M28" s="23"/>
       <c r="N28" s="23"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="7"/>
+      <c r="O28" s="27"/>
+      <c r="P28" s="7">
+        <v>1</v>
+      </c>
       <c r="Q28" s="8"/>
     </row>
     <row r="29" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="22"/>
+      <c r="A29" s="45" t="s">
+        <v>58</v>
+      </c>
       <c r="B29" s="23"/>
       <c r="C29" s="23"/>
       <c r="D29" s="23"/>
@@ -5129,12 +5192,14 @@
       <c r="L29" s="23"/>
       <c r="M29" s="23"/>
       <c r="N29" s="23"/>
-      <c r="O29" s="23"/>
-      <c r="P29" s="5"/>
+      <c r="O29" s="27"/>
+      <c r="P29" s="5">
+        <v>4</v>
+      </c>
       <c r="Q29" s="9"/>
     </row>
     <row r="30" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="26"/>
+      <c r="A30" s="22"/>
       <c r="B30" s="23"/>
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
@@ -5153,7 +5218,7 @@
       <c r="Q30" s="12"/>
     </row>
     <row r="31" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="22"/>
+      <c r="A31" s="25"/>
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
@@ -5172,7 +5237,7 @@
       <c r="Q31" s="9"/>
     </row>
     <row r="32" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="26"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="23"/>
       <c r="C32" s="23"/>
       <c r="D32" s="23"/>
@@ -5191,47 +5256,49 @@
       <c r="Q32" s="12"/>
     </row>
     <row r="33" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="29"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="30"/>
-      <c r="O33" s="30"/>
+      <c r="A33" s="43"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
       <c r="P33" s="13"/>
       <c r="Q33" s="14"/>
     </row>
     <row r="34" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="34"/>
+      <c r="N34" s="34"/>
+      <c r="O34" s="34"/>
       <c r="P34" s="19"/>
       <c r="Q34" s="20"/>
     </row>
     <row r="35" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="26"/>
+      <c r="A35" s="26" t="s">
+        <v>32</v>
+      </c>
       <c r="B35" s="23"/>
       <c r="C35" s="23"/>
       <c r="D35" s="23"/>
@@ -5245,31 +5312,39 @@
       <c r="L35" s="23"/>
       <c r="M35" s="23"/>
       <c r="N35" s="23"/>
-      <c r="O35" s="23"/>
-      <c r="P35" s="7"/>
+      <c r="O35" s="27"/>
+      <c r="P35" s="7">
+        <v>1</v>
+      </c>
       <c r="Q35" s="8"/>
     </row>
     <row r="36" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="22"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="23"/>
-      <c r="M36" s="23"/>
-      <c r="N36" s="23"/>
-      <c r="O36" s="23"/>
-      <c r="P36" s="5"/>
+      <c r="A36" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="46"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="46"/>
+      <c r="J36" s="46"/>
+      <c r="K36" s="46"/>
+      <c r="L36" s="46"/>
+      <c r="M36" s="46"/>
+      <c r="N36" s="46"/>
+      <c r="O36" s="47"/>
+      <c r="P36" s="5">
+        <v>1</v>
+      </c>
       <c r="Q36" s="9"/>
     </row>
     <row r="37" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="26"/>
+      <c r="A37" s="26" t="s">
+        <v>44</v>
+      </c>
       <c r="B37" s="23"/>
       <c r="C37" s="23"/>
       <c r="D37" s="23"/>
@@ -5283,12 +5358,16 @@
       <c r="L37" s="23"/>
       <c r="M37" s="23"/>
       <c r="N37" s="23"/>
-      <c r="O37" s="23"/>
-      <c r="P37" s="7"/>
+      <c r="O37" s="27"/>
+      <c r="P37" s="7">
+        <v>1</v>
+      </c>
       <c r="Q37" s="8"/>
     </row>
     <row r="38" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="22"/>
+      <c r="A38" s="45" t="s">
+        <v>58</v>
+      </c>
       <c r="B38" s="23"/>
       <c r="C38" s="23"/>
       <c r="D38" s="23"/>
@@ -5302,12 +5381,14 @@
       <c r="L38" s="23"/>
       <c r="M38" s="23"/>
       <c r="N38" s="23"/>
-      <c r="O38" s="23"/>
-      <c r="P38" s="5"/>
+      <c r="O38" s="27"/>
+      <c r="P38" s="5">
+        <v>4</v>
+      </c>
       <c r="Q38" s="9"/>
     </row>
     <row r="39" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="26"/>
+      <c r="A39" s="22"/>
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
@@ -5326,7 +5407,7 @@
       <c r="Q39" s="8"/>
     </row>
     <row r="40" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="22"/>
+      <c r="A40" s="25"/>
       <c r="B40" s="23"/>
       <c r="C40" s="23"/>
       <c r="D40" s="23"/>
@@ -5345,7 +5426,7 @@
       <c r="Q40" s="9"/>
     </row>
     <row r="41" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="26"/>
+      <c r="A41" s="22"/>
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
       <c r="D41" s="23"/>
@@ -5364,47 +5445,49 @@
       <c r="Q41" s="8"/>
     </row>
     <row r="42" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="29"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
-      <c r="K42" s="30"/>
-      <c r="L42" s="30"/>
-      <c r="M42" s="30"/>
-      <c r="N42" s="30"/>
-      <c r="O42" s="30"/>
+      <c r="A42" s="43"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
       <c r="P42" s="13"/>
       <c r="Q42" s="14"/>
     </row>
     <row r="43" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="24" t="s">
+      <c r="A43" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="25"/>
-      <c r="J43" s="25"/>
-      <c r="K43" s="25"/>
-      <c r="L43" s="25"/>
-      <c r="M43" s="25"/>
-      <c r="N43" s="25"/>
-      <c r="O43" s="25"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
+      <c r="L43" s="34"/>
+      <c r="M43" s="34"/>
+      <c r="N43" s="34"/>
+      <c r="O43" s="34"/>
       <c r="P43" s="19"/>
       <c r="Q43" s="20"/>
     </row>
     <row r="44" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="26"/>
+      <c r="A44" s="45" t="s">
+        <v>58</v>
+      </c>
       <c r="B44" s="23"/>
       <c r="C44" s="23"/>
       <c r="D44" s="23"/>
@@ -5418,12 +5501,14 @@
       <c r="L44" s="23"/>
       <c r="M44" s="23"/>
       <c r="N44" s="23"/>
-      <c r="O44" s="23"/>
-      <c r="P44" s="7"/>
+      <c r="O44" s="27"/>
+      <c r="P44" s="7">
+        <v>4</v>
+      </c>
       <c r="Q44" s="8"/>
     </row>
     <row r="45" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="22"/>
+      <c r="A45" s="25"/>
       <c r="B45" s="23"/>
       <c r="C45" s="23"/>
       <c r="D45" s="23"/>
@@ -5442,21 +5527,21 @@
       <c r="Q45" s="9"/>
     </row>
     <row r="46" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="32"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
+      <c r="A46" s="31"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="32"/>
+      <c r="O46" s="32"/>
       <c r="P46" s="6"/>
       <c r="Q46" s="10"/>
     </row>
@@ -5480,7 +5565,7 @@
       </c>
       <c r="P47" s="16">
         <f>SUM(P7:P46)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Q47" s="16">
         <f>SUM(Q7:Q46)</f>
@@ -5637,18 +5722,25 @@
     <row r="195" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="A41:O41"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="A37:O37"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="A8:O8"/>
-    <mergeCell ref="A22:O22"/>
-    <mergeCell ref="A17:O17"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="A19:O19"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="N5:Q5"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A38:O38"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A45:O45"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A44:O44"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A40:O40"/>
+    <mergeCell ref="A9:O9"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="A39:O39"/>
+    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="D34:O34"/>
+    <mergeCell ref="A24:O24"/>
     <mergeCell ref="A46:O46"/>
     <mergeCell ref="A18:O18"/>
     <mergeCell ref="D7:O7"/>
@@ -5665,29 +5757,22 @@
     <mergeCell ref="A23:O23"/>
     <mergeCell ref="A32:O32"/>
     <mergeCell ref="L5:M5"/>
+    <mergeCell ref="A41:O41"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="A8:O8"/>
+    <mergeCell ref="A22:O22"/>
+    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="N5:Q5"/>
     <mergeCell ref="D25:O25"/>
     <mergeCell ref="A29:O29"/>
     <mergeCell ref="A35:O35"/>
     <mergeCell ref="A20:O20"/>
-    <mergeCell ref="A38:O38"/>
-    <mergeCell ref="A28:O28"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A45:O45"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A44:O44"/>
-    <mergeCell ref="A31:O31"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A40:O40"/>
-    <mergeCell ref="A9:O9"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="A39:O39"/>
-    <mergeCell ref="A15:O15"/>
-    <mergeCell ref="D34:O34"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="A11:O11"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <pageMargins left="0.62992125984251968" right="0.39370078740157483" top="0.78740157480314965" bottom="0.39370078740157483" header="0.39370078740157483" footer="0"/>
   <pageSetup paperSize="9" scale="99" orientation="portrait"/>
@@ -5713,63 +5798,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="37"/>
     </row>
     <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="36"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="38"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="39"/>
     </row>
     <row r="3" spans="1:17" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="39"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="41"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="42"/>
     </row>
     <row r="4" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2"/>
@@ -5791,11 +5876,11 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="43"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="23"/>
       <c r="E5" s="23"/>
       <c r="F5" s="23"/>
@@ -5803,14 +5888,14 @@
       <c r="H5" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="43"/>
+      <c r="I5" s="24"/>
       <c r="J5" s="23"/>
       <c r="K5" s="23"/>
-      <c r="L5" s="44" t="s">
+      <c r="L5" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="M5" s="37"/>
-      <c r="N5" s="45"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="30"/>
       <c r="O5" s="23"/>
       <c r="P5" s="23"/>
       <c r="Q5" s="23"/>
@@ -5841,28 +5926,28 @@
       </c>
     </row>
     <row r="7" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
       <c r="P7" s="19"/>
       <c r="Q7" s="20"/>
     </row>
     <row r="8" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="42"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
@@ -5876,12 +5961,12 @@
       <c r="L8" s="23"/>
       <c r="M8" s="23"/>
       <c r="N8" s="23"/>
-      <c r="O8" s="28"/>
+      <c r="O8" s="27"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="8"/>
     </row>
     <row r="9" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="27"/>
+      <c r="A9" s="45"/>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
@@ -5895,12 +5980,12 @@
       <c r="L9" s="23"/>
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
-      <c r="O9" s="28"/>
+      <c r="O9" s="27"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="9"/>
     </row>
     <row r="10" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="42"/>
+      <c r="A10" s="26"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
@@ -5914,12 +5999,12 @@
       <c r="L10" s="23"/>
       <c r="M10" s="23"/>
       <c r="N10" s="23"/>
-      <c r="O10" s="28"/>
+      <c r="O10" s="27"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="8"/>
     </row>
     <row r="11" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="27"/>
+      <c r="A11" s="45"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
@@ -5933,12 +6018,12 @@
       <c r="L11" s="23"/>
       <c r="M11" s="23"/>
       <c r="N11" s="23"/>
-      <c r="O11" s="28"/>
+      <c r="O11" s="27"/>
       <c r="P11" s="5"/>
       <c r="Q11" s="9"/>
     </row>
     <row r="12" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="42"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
@@ -5952,12 +6037,12 @@
       <c r="L12" s="23"/>
       <c r="M12" s="23"/>
       <c r="N12" s="23"/>
-      <c r="O12" s="28"/>
+      <c r="O12" s="27"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="12"/>
     </row>
     <row r="13" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="22"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="23"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
@@ -5976,7 +6061,7 @@
       <c r="Q13" s="9"/>
     </row>
     <row r="14" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="42"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="23"/>
       <c r="C14" s="23"/>
       <c r="D14" s="23"/>
@@ -5990,52 +6075,52 @@
       <c r="L14" s="23"/>
       <c r="M14" s="23"/>
       <c r="N14" s="23"/>
-      <c r="O14" s="28"/>
+      <c r="O14" s="27"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="8"/>
     </row>
     <row r="15" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="29"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
+      <c r="A15" s="43"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
       <c r="P15" s="13"/>
       <c r="Q15" s="14"/>
     </row>
     <row r="16" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
       <c r="P16" s="19"/>
       <c r="Q16" s="20"/>
     </row>
     <row r="17" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="26"/>
+      <c r="A17" s="22"/>
       <c r="B17" s="23"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
@@ -6054,7 +6139,7 @@
       <c r="Q17" s="8"/>
     </row>
     <row r="18" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="22"/>
+      <c r="A18" s="25"/>
       <c r="B18" s="23"/>
       <c r="C18" s="23"/>
       <c r="D18" s="23"/>
@@ -6073,7 +6158,7 @@
       <c r="Q18" s="14"/>
     </row>
     <row r="19" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="26"/>
+      <c r="A19" s="22"/>
       <c r="B19" s="23"/>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
@@ -6092,7 +6177,7 @@
       <c r="Q19" s="8"/>
     </row>
     <row r="20" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="22"/>
+      <c r="A20" s="25"/>
       <c r="B20" s="23"/>
       <c r="C20" s="23"/>
       <c r="D20" s="23"/>
@@ -6111,7 +6196,7 @@
       <c r="Q20" s="9"/>
     </row>
     <row r="21" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="26"/>
+      <c r="A21" s="22"/>
       <c r="B21" s="23"/>
       <c r="C21" s="23"/>
       <c r="D21" s="23"/>
@@ -6130,7 +6215,7 @@
       <c r="Q21" s="12"/>
     </row>
     <row r="22" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="22"/>
+      <c r="A22" s="25"/>
       <c r="B22" s="23"/>
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
@@ -6149,7 +6234,7 @@
       <c r="Q22" s="9"/>
     </row>
     <row r="23" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="26"/>
+      <c r="A23" s="22"/>
       <c r="B23" s="23"/>
       <c r="C23" s="23"/>
       <c r="D23" s="23"/>
@@ -6168,47 +6253,47 @@
       <c r="Q23" s="12"/>
     </row>
     <row r="24" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="29"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
+      <c r="A24" s="43"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
       <c r="P24" s="13"/>
       <c r="Q24" s="14"/>
     </row>
     <row r="25" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="25"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="34"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="34"/>
       <c r="P25" s="19"/>
       <c r="Q25" s="20"/>
     </row>
     <row r="26" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="26"/>
+      <c r="A26" s="22"/>
       <c r="B26" s="23"/>
       <c r="C26" s="23"/>
       <c r="D26" s="23"/>
@@ -6227,7 +6312,7 @@
       <c r="Q26" s="8"/>
     </row>
     <row r="27" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="22"/>
+      <c r="A27" s="25"/>
       <c r="B27" s="23"/>
       <c r="C27" s="23"/>
       <c r="D27" s="23"/>
@@ -6246,7 +6331,7 @@
       <c r="Q27" s="14"/>
     </row>
     <row r="28" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="26"/>
+      <c r="A28" s="22"/>
       <c r="B28" s="23"/>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
@@ -6265,7 +6350,7 @@
       <c r="Q28" s="8"/>
     </row>
     <row r="29" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="22"/>
+      <c r="A29" s="25"/>
       <c r="B29" s="23"/>
       <c r="C29" s="23"/>
       <c r="D29" s="23"/>
@@ -6284,7 +6369,7 @@
       <c r="Q29" s="9"/>
     </row>
     <row r="30" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="26"/>
+      <c r="A30" s="22"/>
       <c r="B30" s="23"/>
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
@@ -6303,7 +6388,7 @@
       <c r="Q30" s="12"/>
     </row>
     <row r="31" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="22"/>
+      <c r="A31" s="25"/>
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
@@ -6322,7 +6407,7 @@
       <c r="Q31" s="9"/>
     </row>
     <row r="32" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="26"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="23"/>
       <c r="C32" s="23"/>
       <c r="D32" s="23"/>
@@ -6341,47 +6426,47 @@
       <c r="Q32" s="12"/>
     </row>
     <row r="33" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="29"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="30"/>
-      <c r="O33" s="30"/>
+      <c r="A33" s="43"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
       <c r="P33" s="13"/>
       <c r="Q33" s="14"/>
     </row>
     <row r="34" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="34"/>
+      <c r="N34" s="34"/>
+      <c r="O34" s="34"/>
       <c r="P34" s="19"/>
       <c r="Q34" s="20"/>
     </row>
     <row r="35" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="26"/>
+      <c r="A35" s="22"/>
       <c r="B35" s="23"/>
       <c r="C35" s="23"/>
       <c r="D35" s="23"/>
@@ -6400,7 +6485,7 @@
       <c r="Q35" s="8"/>
     </row>
     <row r="36" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="22"/>
+      <c r="A36" s="25"/>
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
       <c r="D36" s="23"/>
@@ -6419,7 +6504,7 @@
       <c r="Q36" s="9"/>
     </row>
     <row r="37" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="26"/>
+      <c r="A37" s="22"/>
       <c r="B37" s="23"/>
       <c r="C37" s="23"/>
       <c r="D37" s="23"/>
@@ -6438,7 +6523,7 @@
       <c r="Q37" s="8"/>
     </row>
     <row r="38" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="22"/>
+      <c r="A38" s="25"/>
       <c r="B38" s="23"/>
       <c r="C38" s="23"/>
       <c r="D38" s="23"/>
@@ -6457,7 +6542,7 @@
       <c r="Q38" s="9"/>
     </row>
     <row r="39" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="26"/>
+      <c r="A39" s="22"/>
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
@@ -6476,7 +6561,7 @@
       <c r="Q39" s="8"/>
     </row>
     <row r="40" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="22"/>
+      <c r="A40" s="25"/>
       <c r="B40" s="23"/>
       <c r="C40" s="23"/>
       <c r="D40" s="23"/>
@@ -6495,7 +6580,7 @@
       <c r="Q40" s="9"/>
     </row>
     <row r="41" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="26"/>
+      <c r="A41" s="22"/>
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
       <c r="D41" s="23"/>
@@ -6514,47 +6599,47 @@
       <c r="Q41" s="8"/>
     </row>
     <row r="42" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="29"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
-      <c r="K42" s="30"/>
-      <c r="L42" s="30"/>
-      <c r="M42" s="30"/>
-      <c r="N42" s="30"/>
-      <c r="O42" s="30"/>
+      <c r="A42" s="43"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
       <c r="P42" s="13"/>
       <c r="Q42" s="14"/>
     </row>
     <row r="43" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="24" t="s">
+      <c r="A43" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="25"/>
-      <c r="J43" s="25"/>
-      <c r="K43" s="25"/>
-      <c r="L43" s="25"/>
-      <c r="M43" s="25"/>
-      <c r="N43" s="25"/>
-      <c r="O43" s="25"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
+      <c r="L43" s="34"/>
+      <c r="M43" s="34"/>
+      <c r="N43" s="34"/>
+      <c r="O43" s="34"/>
       <c r="P43" s="19"/>
       <c r="Q43" s="20"/>
     </row>
     <row r="44" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="26"/>
+      <c r="A44" s="22"/>
       <c r="B44" s="23"/>
       <c r="C44" s="23"/>
       <c r="D44" s="23"/>
@@ -6573,7 +6658,7 @@
       <c r="Q44" s="8"/>
     </row>
     <row r="45" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="22"/>
+      <c r="A45" s="25"/>
       <c r="B45" s="23"/>
       <c r="C45" s="23"/>
       <c r="D45" s="23"/>
@@ -6592,21 +6677,21 @@
       <c r="Q45" s="9"/>
     </row>
     <row r="46" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="32"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
+      <c r="A46" s="31"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="32"/>
+      <c r="O46" s="32"/>
       <c r="P46" s="6"/>
       <c r="Q46" s="10"/>
     </row>
@@ -6787,18 +6872,25 @@
     <row r="195" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="A41:O41"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="A37:O37"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="A8:O8"/>
-    <mergeCell ref="A22:O22"/>
-    <mergeCell ref="A17:O17"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="A19:O19"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="N5:Q5"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A38:O38"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A45:O45"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A44:O44"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A40:O40"/>
+    <mergeCell ref="A9:O9"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="A39:O39"/>
+    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="D34:O34"/>
+    <mergeCell ref="A24:O24"/>
     <mergeCell ref="A46:O46"/>
     <mergeCell ref="A18:O18"/>
     <mergeCell ref="D7:O7"/>
@@ -6815,29 +6907,22 @@
     <mergeCell ref="A23:O23"/>
     <mergeCell ref="A32:O32"/>
     <mergeCell ref="L5:M5"/>
+    <mergeCell ref="A41:O41"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="A8:O8"/>
+    <mergeCell ref="A22:O22"/>
+    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="N5:Q5"/>
     <mergeCell ref="D25:O25"/>
     <mergeCell ref="A29:O29"/>
     <mergeCell ref="A35:O35"/>
     <mergeCell ref="A20:O20"/>
-    <mergeCell ref="A38:O38"/>
-    <mergeCell ref="A28:O28"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A45:O45"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A44:O44"/>
-    <mergeCell ref="A31:O31"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A40:O40"/>
-    <mergeCell ref="A9:O9"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="A39:O39"/>
-    <mergeCell ref="A15:O15"/>
-    <mergeCell ref="D34:O34"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="A11:O11"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <pageMargins left="0.62992125984251968" right="0.39370078740157483" top="0.78740157480314965" bottom="0.39370078740157483" header="0.39370078740157483" footer="0"/>
   <pageSetup paperSize="9" scale="99" orientation="portrait"/>
